--- a/Excel/Ejercicios/03- datos.xlsx
+++ b/Excel/Ejercicios/03- datos.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuria López Álvarez\Documents\Cursos impartidos\Excel y Power BI\Excel\Ejercicios\Soluciones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\Excel-PowerBI\Excel\Ejercicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2953F742-10C4-43D8-B233-38DF10E9658D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC3F541-024B-46C8-8FF5-70332A4C8D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" xr2:uid="{39DAE768-40BC-4367-B939-C9677852D415}"/>
+    <workbookView xWindow="-113" yWindow="-113" windowWidth="18257" windowHeight="10769" activeTab="2" xr2:uid="{39DAE768-40BC-4367-B939-C9677852D415}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hojas 2" sheetId="2" r:id="rId2"/>
-    <sheet name="Hojas 3" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja 3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -224,9 +224,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -264,7 +264,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -370,7 +370,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -512,7 +512,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -521,7 +521,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{304B42EE-6B1D-4575-A0C8-B7CF70A10381}">
   <dimension ref="A2:H10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
@@ -693,13 +693,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B03CE1-0D06-4FF8-BA22-F6EFA4856666}">
   <dimension ref="A2:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.8984375" customWidth="1"/>
-    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -810,9 +810,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53599861-C142-46B1-AB25-559002546610}">
   <dimension ref="A2:H13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.296875" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
